--- a/islandattrs/data/archipelago_info.xlsx
+++ b/islandattrs/data/archipelago_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\islandattrs_project\islandattrs\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{330A5ACA-E651-46FE-9D79-EDF5CAEA52A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47245E91-1748-40EC-856B-F31720C55B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{F3369DDE-E956-4CF4-A7A3-FB72FE83B4D0}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="253">
   <si>
     <t>卡特群岛（Cat Cays）位于北大西洋，是巴哈马群岛的一部分；位于美国佛罗里达半岛和巴哈马的安德罗斯岛（Andros Island）之间。地理位置为：25°31′7″N-25°34′9″N，79°17′33″W-79°15′31″W。卡特群岛由北卡特岛和南卡特岛组成。其中，北卡特岛面积较大，为1.04km²。卡特群岛总面积为1.38km²，海岸线长15.68km。该数据集是在Google Earth遥感卫星影像及相关的地图基础上研发完成。数据集以.kmz 和.shp 格式存储，压缩后数据量为51.8KB。</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1033,10 +1033,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>中国</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>china</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1066,6 +1062,36 @@
   </si>
   <si>
     <t>南极洲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Asia</t>
+  </si>
+  <si>
+    <t>Europe</t>
+  </si>
+  <si>
+    <t>Africa</t>
+  </si>
+  <si>
+    <t>North America</t>
+  </si>
+  <si>
+    <t>South America</t>
+  </si>
+  <si>
+    <t>Oceania</t>
+  </si>
+  <si>
+    <t>Antarctica</t>
+  </si>
+  <si>
+    <t>图层来源：刘闯, 石瑞香, 张应华, et al. 2015年全球岛(礁)有多少？陆地面积及海岸线长几何？——基于Google Earth遥感影像的数据结果 [J]. 全球变化数据学报(中英文), 2019, 3(02): 124-48+215-39.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图层来源：刘闯, 石瑞香, 张应华, et al. 2015年全球岛(礁)有多少？陆地面积及海岸线长几何？——基于Google Earth遥感影像的数据结果 [J]. 全球变化数据学报(中英文), 2019, 3(02): 124-48+215-39.
+在已上图层间进行裁剪后获得的图层</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1201,12 +1227,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2940,107 +2962,165 @@
       <c r="H72" s="9"/>
       <c r="I72" s="9"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A73" s="11">
+    <row r="73" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A73" s="4">
         <v>72</v>
       </c>
-      <c r="B73" s="12" t="s">
+      <c r="B73" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="C73" s="12" t="s">
+      <c r="C73" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="D73" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="D73" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="E73" s="12">
-        <v>9000</v>
-      </c>
-      <c r="F73" s="9"/>
+      <c r="E73" s="5">
+        <v>6169</v>
+      </c>
+      <c r="F73" s="11" t="s">
+        <v>252</v>
+      </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A74" s="11">
+      <c r="A74" s="4">
         <v>73</v>
       </c>
-      <c r="B74" s="12" t="s">
+      <c r="B74" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E74" s="5">
+        <v>55427</v>
+      </c>
+      <c r="F74" s="9" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A75" s="4">
+        <v>74</v>
+      </c>
+      <c r="B75" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="9"/>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A75" s="11">
-        <v>74</v>
-      </c>
-      <c r="B75" s="12" t="s">
+      <c r="C75" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E75" s="5">
+        <v>239440</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A76" s="4">
+        <v>75</v>
+      </c>
+      <c r="B76" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9"/>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A76" s="11">
-        <v>75</v>
-      </c>
-      <c r="B76" s="12" t="s">
+      <c r="C76" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="E76" s="5">
+        <v>271129</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A77" s="4">
+        <v>76</v>
+      </c>
+      <c r="B77" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
-      <c r="F76" s="9"/>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A77" s="11">
-        <v>76</v>
-      </c>
-      <c r="B77" s="12" t="s">
+      <c r="C77" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="E77" s="5">
+        <v>45387</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A78" s="4">
+        <v>77</v>
+      </c>
+      <c r="B78" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="C77" s="9"/>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="9"/>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A78" s="11">
-        <v>77</v>
-      </c>
-      <c r="B78" s="12" t="s">
+      <c r="C78" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="E78" s="5">
+        <v>11287</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A79" s="4">
+        <v>78</v>
+      </c>
+      <c r="B79" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A79" s="11">
-        <v>78</v>
-      </c>
-      <c r="B79" s="12" t="s">
+      <c r="C79" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="E79" s="5">
+        <v>24999</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A80" s="4">
+        <v>79</v>
+      </c>
+      <c r="B80" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A80" s="11">
-        <v>79</v>
-      </c>
-      <c r="B80" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
+      <c r="C80" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="E80" s="5">
+        <v>9182</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>251</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F72" xr:uid="{E235D35D-D91F-4C3E-BE14-E8C0AC352A65}"/>
